--- a/web/public/forms/orig/o-chakgong-seoryu.xlsx
+++ b/web/public/forms/orig/o-chakgong-seoryu.xlsx
@@ -1202,7 +1202,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6363,7 +6363,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="129" t="inlineStr">
@@ -8080,7 +8080,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="129" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="129" t="inlineStr">
@@ -10423,7 +10423,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="129" t="inlineStr">
@@ -13381,7 +13381,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="129" t="inlineStr">
@@ -15453,7 +15453,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="129" t="inlineStr">
@@ -17321,7 +17321,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -18773,7 +18773,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="129" t="inlineStr">
@@ -20327,7 +20327,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="129" t="inlineStr">
@@ -21696,7 +21696,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="129" t="inlineStr">
@@ -22731,7 +22731,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -23575,7 +23575,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -23699,7 +23699,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -27242,7 +27242,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -30022,7 +30022,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -30973,7 +30973,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -32684,7 +32684,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -34337,7 +34337,7 @@
       </c>
     </row>
     <row r="122" ht="4" customHeight="1"/>
-    <row r="123" ht="68" customHeight="1">
+    <row r="123" ht="83.5" customHeight="1">
       <c r="A123" s="81" t="inlineStr">
         <is>
           <t>공사 중 생기는 폐기물은 종류가 많으나 매각 · 현장 재활용 · 순환골재 활용 등으로 발생량을 최소화하여 쾌적한 공사환경을 만든다. 예기치 못한 상황이나 다량의 폐기물 처리가 필요할 때에 대비해 발주자 · 환경 관련 기관과 꾸준히 협의한다. 현장 종사자에게는 철저한 환경관리가 회사와 사회에 이익이 됨을 알려, 폐기물 처리를 비롯한 환경보전 전반에 책임감을 갖도록 한다.</t>

--- a/web/public/forms/orig/o-chakgong-seoryu.xlsx
+++ b/web/public/forms/orig/o-chakgong-seoryu.xlsx
@@ -1167,7 +1167,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8972,7 +8972,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -12510,7 +12510,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -14930,7 +14930,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -15876,7 +15876,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -17393,7 +17393,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
